--- a/BOM/Induction heater-bom.xlsx
+++ b/BOM/Induction heater-bom.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CAB861-3E01-4978-87F7-BBC3CF5EC6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E200BA-772A-4F9A-8526-679363BF0A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -212,31 +212,39 @@
     <t>https://www.aliexpress.com/item/1005002711238683.html?spm=a2g0o.productlist.main.50.477a4914euPoik&amp;algo_pvid=c910c5e1-95dc-480b-b3f9-444ed5662ba6&amp;algo_exp_id=c910c5e1-95dc-480b-b3f9-444ed5662ba6-49&amp;pdp_ext_f=%7B%22order%22%3A%22145%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21USD%213.88%211.88%21%21%213.88%211.88%21%40211b813b17739477792101402edb6e%2112000021815358235%21sea%21CZ%210%21ABXZ%211%210%21n_tag%3A-29910%3Bd%3A1803c9ff%3Bm03_new_user%3A-29895%3BpisId%3A5000000200562567&amp;curPageLogUid=QgMZjcoePbgO&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005002711238683%7C_p_origin_prod%3A</t>
   </si>
   <si>
-    <t>Mosfet</t>
-  </si>
-  <si>
-    <t>ZVS switching</t>
-  </si>
-  <si>
-    <t>2.10</t>
-  </si>
-  <si>
-    <t>https://www.aliexpress.com/item/1005011797838618.html?spm=a2g0o.productlist.main.21.7a1f1u391u39dq&amp;algo_pvid=5426e889-301e-4c49-bed7-a5b76cfb93be&amp;algo_exp_id=5426e889-301e-4c49-bed7-a5b76cfb93be-20&amp;pdp_ext_f=%7B%22order%22%3A%22-1%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21CZK%2149.77%2149.77%21%21%2115.73%2115.73%21%402103868817739473535908630e97e6%2112000056587455881%21sea%21CZ%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A1803c9ff%3Bm03_new_user%3A-29895&amp;curPageLogUid=f2kKyn5ovPUN&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005011797838618%7C_p_origin_prod%3A</t>
-  </si>
-  <si>
     <t>I have all of the components that are priced as 0, so for these components it is not needed to add them to the BOM.</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005011844869795.html?spm=a2g0o.productlist.main.6.331aK3nTK3nTPQ&amp;algo_pvid=cbc9dd74-dd5a-4a77-907d-66a1834d7ddf&amp;algo_exp_id=cbc9dd74-dd5a-4a77-907d-66a1834d7ddf-5&amp;pdp_ext_f=%7B%22order%22%3A%22-1%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21USD%214.54%214.54%21%21%2131.23%2131.23%21%40210388c917747806068723055e2327%2112000056762259380%21sea%21CZ%216063877758%21X%211%210%21n_tag%3A-29919%3Bd%3A1803c9ff%3Bm03_new_user%3A-29895&amp;curPageLogUid=CfFBsAtcuWCR&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005011844869795%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>5.28</t>
+  </si>
+  <si>
+    <t>Mosfet IRFB7730</t>
+  </si>
+  <si>
+    <t>ZVS switching, 2 pcs needed, best offer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -505,50 +513,53 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="4" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="2" xfId="4" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="60 % – Zvýraznění 1" xfId="4" builtinId="32"/>
@@ -964,7 +975,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I3" s="16"/>
     </row>
@@ -1240,26 +1251,26 @@
     </row>
     <row r="17" spans="1:6" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B17" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="21"/>
+      <c r="A18" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1268,8 +1279,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <ignoredErrors>
-    <ignoredError sqref="C2:D4 C17:D17 C15:C16 C13:D14 C12 C11:D11 C5:C10" numberStoredAsText="1"/>
+    <ignoredError sqref="C2:D4 C17 C15:C16 C13:D14 C12 C11:D11 C5:C10" numberStoredAsText="1"/>
     <ignoredError sqref="D15:D16 D12 D5:D10" twoDigitTextYear="1" numberStoredAsText="1"/>
+    <ignoredError sqref="D17" twoDigitTextYear="1"/>
   </ignoredErrors>
 </worksheet>
 </file>